--- a/assets/downloads/2026-03-15-dotnet-framework-to-dotnet-premigration-checklist.xlsx
+++ b/assets/downloads/2026-03-15-dotnet-framework-to-dotnet-premigration-checklist.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>??????</t>
+          <t>チェック項目</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>????????? 1 ?????</t>
+          <t>なぜ移行するのかを 1 文で言える</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>??????? Windows ??? modern .NET ????????????????????????????</t>
+          <t>今回の着地点が **Windows 専用の modern .NET** なのか、**将来のクロスプラットフォーム化** なのか決まっている</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -529,12 +529,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>target ? .NET ?????????</t>
+          <t>target の .NET バージョンを決めた</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -548,12 +548,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>???????????????EF Core ?????????????????????????</t>
+          <t>今回のスコープに **含めないもの**（EF Core 化、認証刷新、クラウド全面移行など）が決まっている</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -567,12 +567,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>?? .NET Framework ????</t>
+          <t>現行 .NET Framework 側の整備</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>.NET Framework 4.7.2 ??????? 4.8.1 ????</t>
+          <t>.NET Framework 4.7.2 以降、できれば 4.8.1 に寄せた</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -586,12 +586,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>?? .NET Framework ????</t>
+          <t>現行 .NET Framework 側の整備</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>?????????????</t>
+          <t>依存関係を最新寄りへ上げた</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>?? .NET Framework ????</t>
+          <t>現行 .NET Framework 側の整備</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>packages.config ???????</t>
+          <t>`packages.config` の有無を洗った</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -624,12 +624,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>?? .NET Framework ????</t>
+          <t>現行 .NET Framework 側の整備</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PackageReference ?????????</t>
+          <t>`PackageReference` 化の可否を確認した</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -643,12 +643,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>?? .NET Framework ????</t>
+          <t>現行 .NET Framework 側の整備</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SDK ?????????????</t>
+          <t>SDK スタイル化の可否を確認した</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>?? .NET Framework ????</t>
+          <t>現行 .NET Framework 側の整備</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>????????????????????????</t>
+          <t>現行アプリがその状態でビルド・起動・テストできる</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>アプリ種別と技術選定</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>???????? / ?????? / Web / WCF ???????????????</t>
+          <t>クラスライブラリ / デスクトップ / Web / WCF などの種別ごとに難易度を分けた</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -700,12 +700,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>アプリ種別と技術選定</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>WinForms / WPF ? Windows ?????????????</t>
+          <t>WinForms / WPF が Windows 専用のままだと理解している</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>アプリ種別と技術選定</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ASP.NET Framework ? ASP.NET Core ?? app model ??????????</t>
+          <t>ASP.NET Framework は ASP.NET Core への app model 移行だと理解している</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>アプリ種別と技術選定</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Web Forms ? UI ????????????</t>
+          <t>Web Forms の UI 層置換を見積もりに入れた</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -757,12 +757,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>??????????</t>
+          <t>アプリ種別と技術選定</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>WCF ????????????????????</t>
+          <t>WCF はクライアントとサーバーを分けて評価した</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>????????? API</t>
+          <t>非対応技術・要注意 API</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AppDomain ??????</t>
+          <t>`AppDomain` 依存を洗った</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -795,12 +795,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>????????? API</t>
+          <t>非対応技術・要注意 API</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Remoting / MarshalByRefObject / BeginInvoke / EndInvoke ????</t>
+          <t>Remoting / `MarshalByRefObject` / `BeginInvoke` / `EndInvoke` を洗った</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>????????? API</t>
+          <t>非対応技術・要注意 API</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CAS / Security Transparency / COM+ / WF ????</t>
+          <t>CAS / Security Transparency / COM+ / WF を洗った</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -833,12 +833,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>????????? API</t>
+          <t>非対応技術・要注意 API</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>BinaryFormatter ??????</t>
+          <t>BinaryFormatter 依存を洗った</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -852,12 +852,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>????????? API</t>
+          <t>非対応技術・要注意 API</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>System.Web ??????</t>
+          <t>`System.Web` 依存を洗った</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -871,12 +871,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Windows ????</t>
+          <t>Windows 専用依存</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>??????WMI?EventLog?Windows Service?Directory Services ???????</t>
+          <t>レジストリ、WMI、EventLog、Windows Service、Directory Services の利用を洗った</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -890,12 +890,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Windows ????</t>
+          <t>Windows 専用依存</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>System.Drawing.Common ???????</t>
+          <t>`System.Drawing.Common` の利用を洗った</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -909,12 +909,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Windows ????</t>
+          <t>Windows 専用依存</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COM / ActiveX / Office Interop / P/Invoke / ????? DLL ????</t>
+          <t>COM / ActiveX / Office Interop / P/Invoke / ネイティブ DLL を洗った</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -928,12 +928,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Windows ????</t>
+          <t>Windows 専用依存</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>x86 / x64 / ARM64 ????????</t>
+          <t>x86 / x64 / ARM64 の制約を確認した</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>shared library ????????</t>
+          <t>shared library とデータアクセス</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>shared library ??????? / app model ????????</t>
+          <t>shared library を **業務ロジック / app model 密着層** に分類した</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>shared library ????????</t>
+          <t>shared library とデータアクセス</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>netstandard2.0 ??????????</t>
+          <t>`netstandard2.0` 化できるものを洗った</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
@@ -985,12 +985,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>shared library ????????</t>
+          <t>shared library とデータアクセス</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>multi-target ?????????????</t>
+          <t>multi-target が必要なライブラリを洗った</t>
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>shared library ????????</t>
+          <t>shared library とデータアクセス</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EF6 ???? runtime ????????????</t>
+          <t>EF6 を残して runtime だけ先に移せるか判断した</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>shared library ????????</t>
+          <t>shared library とデータアクセス</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EDMX / Designer ???????</t>
+          <t>EDMX / Designer 依存を確認した</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>??? build</t>
+          <t>運用と build</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>?????????????</t>
+          <t>設定ファイルの棚卸しをした</t>
         </is>
       </c>
       <c r="D31" s="2" t="n"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>??? build</t>
+          <t>運用と build</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>?????IIS / Service / MSI / ClickOnce ????????</t>
+          <t>配布方式（IIS / Service / MSI / ClickOnce など）を確認した</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>??? build</t>
+          <t>運用と build</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>?? / ?? / ?? / ??????????????</t>
+          <t>ログ / 監視 / 権限 / 実行アカウント前提を確認した</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>??? build</t>
+          <t>運用と build</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CI/CD ? build agent ???????????</t>
+          <t>CI/CD と build agent の更新が必要か確認した</t>
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>??? build</t>
+          <t>運用と build</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>????????????</t>
+          <t>ロールバック手順を作った</t>
         </is>
       </c>
       <c r="D35" s="2" t="n"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>We have decided whether the landing zone is Windows-only modern .NET or future cross-platform</t>
+          <t>We have decided whether the landing zone is **Windows-only modern .NET** or **future cross-platform**</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>We have explicitly listed what is out of scope for this phase, such as EF Core migration, auth redesign, or full cloud relocation</t>
+          <t>We have explicitly listed what is **out of scope** for this phase, such as EF Core migration, auth redesign, or full cloud relocation</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>We checked where packages.config still exists</t>
+          <t>We checked where `packages.config` still exists</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>We evaluated PackageReference conversion feasibility</t>
+          <t>We evaluated `PackageReference` conversion feasibility</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>We audited Remoting, MarshalByRefObject, BeginInvoke, and EndInvoke</t>
+          <t>We audited Remoting, `MarshalByRefObject`, `BeginInvoke`, and `EndInvoke`</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>We audited System.Web dependency</t>
+          <t>We audited `System.Web` dependency</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>We audited System.Drawing.Common usage</t>
+          <t>We audited `System.Drawing.Common` usage</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>We checked x86, x64, and ARM64 restrictions</t>
+          <t>We checked `x86`, `x64`, and `ARM64` restrictions</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>We identified libraries that can move to netstandard2.0</t>
+          <t>We identified libraries that can move to `netstandard2.0`</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
